--- a/periapuranam/day_wise_plan.xlsx
+++ b/periapuranam/day_wise_plan.xlsx
@@ -41,7 +41,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+  </numFmts>
   <fonts count="13">
     <font>
       <name val="Calibri"/>
@@ -116,7 +118,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="14">
     <fill>
       <patternFill/>
     </fill>
@@ -183,6 +185,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFE699"/>
         <bgColor rgb="00FFE699"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -270,7 +278,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -362,6 +370,21 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="12" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -966,16 +989,34 @@
           <t>$1.89</t>
         </is>
       </c>
-      <c r="J4" s="5" t="inlineStr"/>
-      <c r="K4" s="5" t="inlineStr"/>
-      <c r="L4" s="5" t="inlineStr"/>
-      <c r="M4" s="5" t="inlineStr"/>
+      <c r="J4" s="36" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="inlineStr">
+        <is>
+          <t>56/56</t>
+        </is>
+      </c>
+      <c r="L4" s="5" t="inlineStr">
+        <is>
+          <t>~5.2h seq (217 chunks) + 11 translate</t>
+        </is>
+      </c>
+      <c r="M4" s="5" t="n">
+        <v>2.30449</v>
+      </c>
       <c r="N4" s="4" t="inlineStr">
         <is>
-          <t>11 stories Medium batch</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr"/>
+          <t>11/11 PASS Chapter 4/5/6=ok no ==== finish:stop; viran_mindar Chapter05 loop fixed 42k-&gt;11k + removed stray Chapter 8; perumizhala resumed after network drop; verify Human Verified No pending spot-listen</t>
+        </is>
+      </c>
+      <c r="O4" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="52" customHeight="1">
       <c r="A5" s="2" t="n">
@@ -2183,7 +2224,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2525,6 +2566,71 @@
       <c r="M5" s="35" t="inlineStr">
         <is>
           <t>INFO — keep flagged</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="39" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="39" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C6" s="39" t="inlineStr">
+        <is>
+          <t>Day 3</t>
+        </is>
+      </c>
+      <c r="D6" s="39" t="inlineStr">
+        <is>
+          <t>Viran Mindar Nayanar</t>
+        </is>
+      </c>
+      <c r="E6" s="39" t="inlineStr">
+        <is>
+          <t>Viran Mindar Nayanar</t>
+        </is>
+      </c>
+      <c r="F6" s="39" t="inlineStr">
+        <is>
+          <t>85,86,87,88,89,90 (Chapter 05 affected)</t>
+        </is>
+      </c>
+      <c r="G6" s="39" t="inlineStr">
+        <is>
+          <t>1SZcVJk3o46mKgshCnfTRpnHr9Zu96h7S et al. (seq 85-90; affected English Chapter 05)</t>
+        </is>
+      </c>
+      <c r="H6" s="39" t="inlineStr">
+        <is>
+          <t>viran_mindar_nayanar</t>
+        </is>
+      </c>
+      <c r="I6" s="39" t="inlineStr">
+        <is>
+          <t>periapuranam/output/day-03/viran_mindar_nayanar/viran_mindar_nayanar_english.txt</t>
+        </is>
+      </c>
+      <c r="J6" s="39" t="inlineStr">
+        <is>
+          <t>TRANSLATION HALLUCINATION + stray header</t>
+        </is>
+      </c>
+      <c r="K6" s="39" t="inlineStr">
+        <is>
+          <t>English Chapter 05 returned 42,594 chars with 1482x "Thirumoolattanam" / 1479x "in Thirumoolattanam," loop (vs Tamil 11,483). Also stray "Chapter 8, Religion..." block (1,111 chars) between Chapter 02 and 03. Story length inflated 94,947 vs correct 62,819. Classic Gemini 2.5-flash repetition loop.</t>
+        </is>
+      </c>
+      <c r="L6" s="39" t="inlineStr">
+        <is>
+          <t>Fixed 2026-09-14: Re-translated Tamil Chapter 05 alone (temp 0.3, 15k tokens) -&gt; 11,573 chars 1x Thirumoolattanam; removed stray Chapter 8 block; rebuilt english (62,819) + bilingual (234,598) + meta fix note. Verified 6ch, no ====, finish:stop. Keep for batch anomaly review in end.</t>
+        </is>
+      </c>
+      <c r="M6" s="40" t="inlineStr">
+        <is>
+          <t>FIXED 2026-09-14 - keep flagged for final review</t>
         </is>
       </c>
     </row>
@@ -5721,26 +5827,44 @@
           <t>muruga_nayanar</t>
         </is>
       </c>
-      <c r="I3" s="23" t="inlineStr">
-        <is>
-          <t>To be done</t>
-        </is>
-      </c>
-      <c r="J3" s="21" t="inlineStr"/>
-      <c r="K3" s="21" t="inlineStr"/>
-      <c r="L3" s="22" t="inlineStr"/>
-      <c r="M3" s="22" t="inlineStr"/>
-      <c r="N3" s="22" t="inlineStr"/>
+      <c r="I3" s="38" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J3" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="K3" s="21" t="n">
+        <v>16</v>
+      </c>
+      <c r="L3" s="22" t="n">
+        <v>0.1184</v>
+      </c>
+      <c r="M3" s="22" t="n">
+        <v>0.03379</v>
+      </c>
+      <c r="N3" s="22" t="n">
+        <v>0.15219</v>
+      </c>
       <c r="O3" s="21" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P3" s="22" t="inlineStr"/>
-      <c r="Q3" s="22" t="inlineStr"/>
+      <c r="P3" s="22" t="inlineStr">
+        <is>
+          <t>0 retries, all chunks OK</t>
+        </is>
+      </c>
+      <c r="Q3" s="22" t="inlineStr">
+        <is>
+          <t>Tamil 44694 chars /122651 bytes 4ch no ====; English 49473 chars finish:stop; total $0.15219</t>
+        </is>
+      </c>
       <c r="R3" s="22" t="inlineStr">
         <is>
-          <t>periapuranam/output/muruga_nayanar/tamil_real/muruga_nayanar_tamil.txt ; muruga_nayanar_english.txt</t>
+          <t>periapuranam/output/day-03/muruga_nayanar/tamil_real/muruga_nayanar_tamil.txt ; muruga_nayanar_english.txt</t>
         </is>
       </c>
     </row>
@@ -5779,26 +5903,44 @@
           <t>muzhu_neeru_poosiya_munivar</t>
         </is>
       </c>
-      <c r="I4" s="23" t="inlineStr">
-        <is>
-          <t>To be done</t>
-        </is>
-      </c>
-      <c r="J4" s="21" t="inlineStr"/>
-      <c r="K4" s="21" t="inlineStr"/>
-      <c r="L4" s="22" t="inlineStr"/>
-      <c r="M4" s="22" t="inlineStr"/>
-      <c r="N4" s="22" t="inlineStr"/>
+      <c r="I4" s="38" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J4" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="K4" s="21" t="n">
+        <v>15</v>
+      </c>
+      <c r="L4" s="22" t="n">
+        <v>0.12906</v>
+      </c>
+      <c r="M4" s="22" t="n">
+        <v>0.0377</v>
+      </c>
+      <c r="N4" s="22" t="n">
+        <v>0.16676</v>
+      </c>
       <c r="O4" s="21" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P4" s="22" t="inlineStr"/>
-      <c r="Q4" s="22" t="inlineStr"/>
+      <c r="P4" s="22" t="inlineStr">
+        <is>
+          <t>0 retries, all chunks OK</t>
+        </is>
+      </c>
+      <c r="Q4" s="22" t="inlineStr">
+        <is>
+          <t>Tamil 50653 chars /138556 bytes 4ch no ====; English 54429 chars finish:stop; total $0.16676</t>
+        </is>
+      </c>
       <c r="R4" s="22" t="inlineStr">
         <is>
-          <t>periapuranam/output/muzhu_neeru_poosiya_munivar/tamil_real/muzhu_neeru_poosiya_munivar_tamil.txt ; muzhu_neeru_poosiya_munivar_english.txt</t>
+          <t>periapuranam/output/day-03/muzhu_neeru_poosiya_munivar/tamil_real/muzhu_neeru_poosiya_munivar_tamil.txt ; muzhu_neeru_poosiya_munivar_english.txt</t>
         </is>
       </c>
     </row>
@@ -5837,26 +5979,44 @@
           <t>pugazh_chozha_nayanar</t>
         </is>
       </c>
-      <c r="I5" s="23" t="inlineStr">
-        <is>
-          <t>To be done</t>
-        </is>
-      </c>
-      <c r="J5" s="21" t="inlineStr"/>
-      <c r="K5" s="21" t="inlineStr"/>
-      <c r="L5" s="22" t="inlineStr"/>
-      <c r="M5" s="22" t="inlineStr"/>
-      <c r="N5" s="22" t="inlineStr"/>
+      <c r="I5" s="38" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J5" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="K5" s="21" t="n">
+        <v>14</v>
+      </c>
+      <c r="L5" s="22" t="n">
+        <v>0.10649</v>
+      </c>
+      <c r="M5" s="22" t="n">
+        <v>0.02946</v>
+      </c>
+      <c r="N5" s="22" t="n">
+        <v>0.13595</v>
+      </c>
       <c r="O5" s="21" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P5" s="22" t="inlineStr"/>
-      <c r="Q5" s="22" t="inlineStr"/>
+      <c r="P5" s="22" t="inlineStr">
+        <is>
+          <t>0 retries, all chunks OK</t>
+        </is>
+      </c>
+      <c r="Q5" s="22" t="inlineStr">
+        <is>
+          <t>Tamil 41532 chars /112724 bytes 4ch no ====; English 41532 chars finish:stop; total $0.13595</t>
+        </is>
+      </c>
       <c r="R5" s="22" t="inlineStr">
         <is>
-          <t>periapuranam/output/pugazh_chozha_nayanar/tamil_real/pugazh_chozha_nayanar_tamil.txt ; pugazh_chozha_nayanar_english.txt</t>
+          <t>periapuranam/output/day-03/pugazh_chozha_nayanar/tamil_real/pugazh_chozha_nayanar_tamil.txt ; pugazh_chozha_nayanar_english.txt</t>
         </is>
       </c>
     </row>
@@ -5895,26 +6055,44 @@
           <t>chithaththaich_sivan_pale_vaiththar</t>
         </is>
       </c>
-      <c r="I6" s="23" t="inlineStr">
-        <is>
-          <t>To be done</t>
-        </is>
-      </c>
-      <c r="J6" s="21" t="inlineStr"/>
-      <c r="K6" s="21" t="inlineStr"/>
-      <c r="L6" s="22" t="inlineStr"/>
-      <c r="M6" s="22" t="inlineStr"/>
-      <c r="N6" s="22" t="inlineStr"/>
+      <c r="I6" s="38" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J6" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="K6" s="21" t="n">
+        <v>20</v>
+      </c>
+      <c r="L6" s="22" t="n">
+        <v>0.17726</v>
+      </c>
+      <c r="M6" s="22" t="n">
+        <v>0.0491</v>
+      </c>
+      <c r="N6" s="22" t="n">
+        <v>0.22636</v>
+      </c>
       <c r="O6" s="21" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P6" s="22" t="inlineStr"/>
-      <c r="Q6" s="22" t="inlineStr"/>
+      <c r="P6" s="22" t="inlineStr">
+        <is>
+          <t>0 retries, all chunks OK</t>
+        </is>
+      </c>
+      <c r="Q6" s="22" t="inlineStr">
+        <is>
+          <t>Tamil 65514 chars /178569 bytes 5ch no ====; English 74889 chars finish:stop; total $0.22636</t>
+        </is>
+      </c>
       <c r="R6" s="22" t="inlineStr">
         <is>
-          <t>periapuranam/output/chithaththaich_sivan_pale_vaiththar/tamil_real/chithaththaich_sivan_pale_vaiththar_tamil.txt ; chithaththaich_sivan_pale_vaiththar_english.txt</t>
+          <t>periapuranam/output/day-03/chithaththaich_sivan_pale_vaiththar/tamil_real/chithaththaich_sivan_pale_vaiththar_tamil.txt ; chithaththaich_sivan_pale_vaiththar_english.txt</t>
         </is>
       </c>
     </row>
@@ -5953,26 +6131,44 @@
           <t>dhandi_adigal_nayanar</t>
         </is>
       </c>
-      <c r="I7" s="23" t="inlineStr">
-        <is>
-          <t>To be done</t>
-        </is>
-      </c>
-      <c r="J7" s="21" t="inlineStr"/>
-      <c r="K7" s="21" t="inlineStr"/>
-      <c r="L7" s="22" t="inlineStr"/>
-      <c r="M7" s="22" t="inlineStr"/>
-      <c r="N7" s="22" t="inlineStr"/>
+      <c r="I7" s="38" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J7" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="K7" s="21" t="n">
+        <v>24</v>
+      </c>
+      <c r="L7" s="22" t="n">
+        <v>0.21459</v>
+      </c>
+      <c r="M7" s="22" t="n">
+        <v>0.06136</v>
+      </c>
+      <c r="N7" s="22" t="n">
+        <v>0.27595</v>
+      </c>
       <c r="O7" s="21" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P7" s="22" t="inlineStr"/>
-      <c r="Q7" s="22" t="inlineStr"/>
+      <c r="P7" s="22" t="inlineStr">
+        <is>
+          <t>0 retries, all chunks OK</t>
+        </is>
+      </c>
+      <c r="Q7" s="22" t="inlineStr">
+        <is>
+          <t>Tamil 80590 chars /220757 bytes 5ch no ====; English 88826 chars finish:stop; total $0.27595</t>
+        </is>
+      </c>
       <c r="R7" s="22" t="inlineStr">
         <is>
-          <t>periapuranam/output/dhandi_adigal_nayanar/tamil_real/dhandi_adigal_nayanar_tamil.txt ; dhandi_adigal_nayanar_english.txt</t>
+          <t>periapuranam/output/day-03/dhandi_adigal_nayanar/tamil_real/dhandi_adigal_nayanar_tamil.txt ; dhandi_adigal_nayanar_english.txt</t>
         </is>
       </c>
     </row>
@@ -6011,26 +6207,44 @@
           <t>perumizhalaikurumba_nayanar</t>
         </is>
       </c>
-      <c r="I8" s="23" t="inlineStr">
-        <is>
-          <t>To be done</t>
-        </is>
-      </c>
-      <c r="J8" s="21" t="inlineStr"/>
-      <c r="K8" s="21" t="inlineStr"/>
-      <c r="L8" s="22" t="inlineStr"/>
-      <c r="M8" s="22" t="inlineStr"/>
-      <c r="N8" s="22" t="inlineStr"/>
+      <c r="I8" s="38" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J8" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="K8" s="21" t="n">
+        <v>18</v>
+      </c>
+      <c r="L8" s="22" t="n">
+        <v>0.15865</v>
+      </c>
+      <c r="M8" s="22" t="n">
+        <v>0.04071</v>
+      </c>
+      <c r="N8" s="22" t="n">
+        <v>0.19936</v>
+      </c>
       <c r="O8" s="21" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P8" s="22" t="inlineStr"/>
-      <c r="Q8" s="22" t="inlineStr"/>
+      <c r="P8" s="22" t="inlineStr">
+        <is>
+          <t>1 retry ConnectionReset 10054 chunk01 auto-recovered; resumed from 483 partial</t>
+        </is>
+      </c>
+      <c r="Q8" s="22" t="inlineStr">
+        <is>
+          <t>Tamil 58220 chars /160077 bytes 5ch no ====; English 58138 chars finish:stop; total $0.19936</t>
+        </is>
+      </c>
       <c r="R8" s="22" t="inlineStr">
         <is>
-          <t>periapuranam/output/perumizhalaikurumba_nayanar/tamil_real/perumizhalaikurumba_nayanar_tamil.txt ; perumizhalaikurumba_nayanar_english.txt</t>
+          <t>periapuranam/output/day-03/perumizhalaikurumba_nayanar/tamil_real/perumizhalaikurumba_nayanar_tamil.txt ; perumizhalaikurumba_nayanar_english.txt</t>
         </is>
       </c>
     </row>
@@ -6069,26 +6283,44 @@
           <t>rudhra_pasupadhi_nayanar</t>
         </is>
       </c>
-      <c r="I9" s="23" t="inlineStr">
-        <is>
-          <t>To be done</t>
-        </is>
-      </c>
-      <c r="J9" s="21" t="inlineStr"/>
-      <c r="K9" s="21" t="inlineStr"/>
-      <c r="L9" s="22" t="inlineStr"/>
-      <c r="M9" s="22" t="inlineStr"/>
-      <c r="N9" s="22" t="inlineStr"/>
+      <c r="I9" s="38" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J9" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="K9" s="21" t="n">
+        <v>18</v>
+      </c>
+      <c r="L9" s="22" t="n">
+        <v>0.13727</v>
+      </c>
+      <c r="M9" s="22" t="n">
+        <v>0.03606</v>
+      </c>
+      <c r="N9" s="22" t="n">
+        <v>0.17333</v>
+      </c>
       <c r="O9" s="21" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P9" s="22" t="inlineStr"/>
-      <c r="Q9" s="22" t="inlineStr"/>
+      <c r="P9" s="22" t="inlineStr">
+        <is>
+          <t>0 retries, all chunks OK</t>
+        </is>
+      </c>
+      <c r="Q9" s="22" t="inlineStr">
+        <is>
+          <t>Tamil 49083 chars /134438 bytes 5ch no ====; English 51607 chars finish:stop; total $0.17333</t>
+        </is>
+      </c>
       <c r="R9" s="22" t="inlineStr">
         <is>
-          <t>periapuranam/output/rudhra_pasupadhi_nayanar/tamil_real/rudhra_pasupadhi_nayanar_tamil.txt ; rudhra_pasupadhi_nayanar_english.txt</t>
+          <t>periapuranam/output/day-03/rudhra_pasupadhi_nayanar/tamil_real/rudhra_pasupadhi_nayanar_tamil.txt ; rudhra_pasupadhi_nayanar_english.txt</t>
         </is>
       </c>
     </row>
@@ -6127,26 +6359,44 @@
           <t>eanati_nathar_nayanar</t>
         </is>
       </c>
-      <c r="I10" s="23" t="inlineStr">
-        <is>
-          <t>To be done</t>
-        </is>
-      </c>
-      <c r="J10" s="21" t="inlineStr"/>
-      <c r="K10" s="21" t="inlineStr"/>
-      <c r="L10" s="22" t="inlineStr"/>
-      <c r="M10" s="22" t="inlineStr"/>
-      <c r="N10" s="22" t="inlineStr"/>
+      <c r="I10" s="38" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J10" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="K10" s="21" t="n">
+        <v>24</v>
+      </c>
+      <c r="L10" s="22" t="n">
+        <v>0.2021</v>
+      </c>
+      <c r="M10" s="22" t="n">
+        <v>0.04804</v>
+      </c>
+      <c r="N10" s="22" t="n">
+        <v>0.25014</v>
+      </c>
       <c r="O10" s="21" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P10" s="22" t="inlineStr"/>
-      <c r="Q10" s="22" t="inlineStr"/>
+      <c r="P10" s="22" t="inlineStr">
+        <is>
+          <t>0 retries, all chunks OK</t>
+        </is>
+      </c>
+      <c r="Q10" s="22" t="inlineStr">
+        <is>
+          <t>Tamil 71655 chars /195984 bytes 6ch no ====; English 71943 chars finish:stop; total $0.25014</t>
+        </is>
+      </c>
       <c r="R10" s="22" t="inlineStr">
         <is>
-          <t>periapuranam/output/eanati_nathar_nayanar/tamil_real/eanati_nathar_nayanar_tamil.txt ; eanati_nathar_nayanar_english.txt</t>
+          <t>periapuranam/output/day-03/eanati_nathar_nayanar/tamil_real/eanati_nathar_nayanar_tamil.txt ; eanati_nathar_nayanar_english.txt</t>
         </is>
       </c>
     </row>
@@ -6185,26 +6435,44 @@
           <t>manakkanchara_nayanar</t>
         </is>
       </c>
-      <c r="I11" s="23" t="inlineStr">
-        <is>
-          <t>To be done</t>
-        </is>
-      </c>
-      <c r="J11" s="21" t="inlineStr"/>
-      <c r="K11" s="21" t="inlineStr"/>
-      <c r="L11" s="22" t="inlineStr"/>
-      <c r="M11" s="22" t="inlineStr"/>
-      <c r="N11" s="22" t="inlineStr"/>
+      <c r="I11" s="38" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J11" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="K11" s="21" t="n">
+        <v>22</v>
+      </c>
+      <c r="L11" s="22" t="n">
+        <v>0.19038</v>
+      </c>
+      <c r="M11" s="22" t="n">
+        <v>0.04927</v>
+      </c>
+      <c r="N11" s="22" t="n">
+        <v>0.23965</v>
+      </c>
       <c r="O11" s="21" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P11" s="22" t="inlineStr"/>
-      <c r="Q11" s="22" t="inlineStr"/>
+      <c r="P11" s="22" t="inlineStr">
+        <is>
+          <t>0 retries, all chunks OK</t>
+        </is>
+      </c>
+      <c r="Q11" s="22" t="inlineStr">
+        <is>
+          <t>Tamil 67618 chars /185695 bytes 6ch no ====; English 70503 chars finish:stop; total $0.23965</t>
+        </is>
+      </c>
       <c r="R11" s="22" t="inlineStr">
         <is>
-          <t>periapuranam/output/manakkanchara_nayanar/tamil_real/manakkanchara_nayanar_tamil.txt ; manakkanchara_nayanar_english.txt</t>
+          <t>periapuranam/output/day-03/manakkanchara_nayanar/tamil_real/manakkanchara_nayanar_tamil.txt ; manakkanchara_nayanar_english.txt</t>
         </is>
       </c>
     </row>
@@ -6243,26 +6511,44 @@
           <t>mara_nayanar</t>
         </is>
       </c>
-      <c r="I12" s="23" t="inlineStr">
-        <is>
-          <t>To be done</t>
-        </is>
-      </c>
-      <c r="J12" s="21" t="inlineStr"/>
-      <c r="K12" s="21" t="inlineStr"/>
-      <c r="L12" s="22" t="inlineStr"/>
-      <c r="M12" s="22" t="inlineStr"/>
-      <c r="N12" s="22" t="inlineStr"/>
+      <c r="I12" s="38" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J12" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="K12" s="21" t="n">
+        <v>24</v>
+      </c>
+      <c r="L12" s="22" t="n">
+        <v>0.19646</v>
+      </c>
+      <c r="M12" s="22" t="n">
+        <v>0.04678</v>
+      </c>
+      <c r="N12" s="22" t="n">
+        <v>0.24324</v>
+      </c>
       <c r="O12" s="21" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P12" s="22" t="inlineStr"/>
-      <c r="Q12" s="22" t="inlineStr"/>
+      <c r="P12" s="22" t="inlineStr">
+        <is>
+          <t>0 retries, all chunks OK</t>
+        </is>
+      </c>
+      <c r="Q12" s="22" t="inlineStr">
+        <is>
+          <t>Tamil 72124 chars /197919 bytes 6ch no ====; English 71030 chars finish:stop; total $0.24324</t>
+        </is>
+      </c>
       <c r="R12" s="22" t="inlineStr">
         <is>
-          <t>periapuranam/output/mara_nayanar/tamil_real/mara_nayanar_tamil.txt ; mara_nayanar_english.txt</t>
+          <t>periapuranam/output/day-03/mara_nayanar/tamil_real/mara_nayanar_tamil.txt ; mara_nayanar_english.txt</t>
         </is>
       </c>
     </row>
@@ -6301,26 +6587,44 @@
           <t>viran_mindar</t>
         </is>
       </c>
-      <c r="I13" s="23" t="inlineStr">
-        <is>
-          <t>To be done</t>
-        </is>
-      </c>
-      <c r="J13" s="21" t="inlineStr"/>
-      <c r="K13" s="21" t="inlineStr"/>
-      <c r="L13" s="22" t="inlineStr"/>
-      <c r="M13" s="22" t="inlineStr"/>
-      <c r="N13" s="22" t="inlineStr"/>
+      <c r="I13" s="38" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J13" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="K13" s="21" t="n">
+        <v>22</v>
+      </c>
+      <c r="L13" s="22" t="n">
+        <v>0.17292</v>
+      </c>
+      <c r="M13" s="22" t="n">
+        <v>0.06864000000000001</v>
+      </c>
+      <c r="N13" s="22" t="n">
+        <v>0.24156</v>
+      </c>
       <c r="O13" s="21" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P13" s="22" t="inlineStr"/>
-      <c r="Q13" s="22" t="inlineStr"/>
+      <c r="P13" s="22" t="inlineStr">
+        <is>
+          <t>1 fix: Chapter05 1479x Thirumoolattanam loop re-translated</t>
+        </is>
+      </c>
+      <c r="Q13" s="22" t="inlineStr">
+        <is>
+          <t>Tamil 62406 chars /171695 bytes 6ch no ====; English 62819 chars finish:stop; total $0.24156 FIXED Chapter05 loop removed, stray Chapter 8 removed (94k-&gt;62k)</t>
+        </is>
+      </c>
       <c r="R13" s="22" t="inlineStr">
         <is>
-          <t>periapuranam/output/viran_mindar/tamil_real/viran_mindar_tamil.txt ; viran_mindar_english.txt</t>
+          <t>periapuranam/output/day-03/viran_mindar_nayanar/tamil_real/viran_mindar_nayanar_tamil.txt ; viran_mindar_nayanar_english.txt</t>
         </is>
       </c>
     </row>

--- a/periapuranam/day_wise_plan.xlsx
+++ b/periapuranam/day_wise_plan.xlsx
@@ -1051,19 +1051,33 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>$1.88</t>
-        </is>
-      </c>
-      <c r="J5" s="5" t="inlineStr"/>
-      <c r="K5" s="5" t="inlineStr"/>
-      <c r="L5" s="5" t="inlineStr"/>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>56/56</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>223 chunks 2-workers + fixes</t>
+        </is>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>2.3147</v>
+      </c>
       <c r="M5" s="5" t="inlineStr"/>
       <c r="N5" s="4" t="inlineStr">
         <is>
-          <t>Anaya already done - reuse Sakkiya 8, IyarPakai 9</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr"/>
+          <t>Day4 7/7 PASS Chapter N==files no ====; ThiruMoola/Tiru 0 anomalies dur-aware; Mei 083 fixed; Iyar HUGE fixed; Sak chunked translate</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="52" customHeight="1">
       <c r="A6" s="2" t="n">
@@ -6807,7 +6821,7 @@
         </is>
       </c>
       <c r="J3" s="27" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K3" s="27" t="n">
         <v>25</v>
@@ -6816,10 +6830,10 @@
         <v>0.2</v>
       </c>
       <c r="M3" s="27" t="n">
-        <v>0.045353979</v>
+        <v>0.0454</v>
       </c>
       <c r="N3" s="27" t="n">
-        <v>0.24535</v>
+        <v>0.2454</v>
       </c>
       <c r="O3" s="27" t="inlineStr">
         <is>
@@ -6828,12 +6842,12 @@
       </c>
       <c r="P3" s="25" t="inlineStr">
         <is>
-          <t>0 retries — pilot verified, real audio → Tamil via gemini-2.5-flash 300s chunks</t>
+          <t>0 retries — pilot 083_chunk02 0c fixed 3474c</t>
         </is>
       </c>
       <c r="Q3" s="25" t="inlineStr">
         <is>
-          <t>PILOT — Already done in _test_merge/anaya_nayanar/ (seq 173-179, 6 unique files, 7 catalog rows, duplicate 175 same as 174). Verified Tamil 64845 chars /177KB, English 66881 chars, Chapter 01..06 no ==== . Remains in _test_merge for now; don't re-run until Day 4 batch. Promote to output/anaya_nayanar/ only after Day 9 QA.</t>
+          <t>PROMOTED 2026-09-15 _test_merge-&gt;output/day-04 + dur-aware instrumentation</t>
         </is>
       </c>
       <c r="R3" s="25" t="inlineStr">
@@ -6879,21 +6893,39 @@
       </c>
       <c r="I4" s="23" t="inlineStr">
         <is>
-          <t>To be done</t>
-        </is>
-      </c>
-      <c r="J4" s="21" t="inlineStr"/>
-      <c r="K4" s="21" t="inlineStr"/>
-      <c r="L4" s="22" t="inlineStr"/>
-      <c r="M4" s="22" t="inlineStr"/>
-      <c r="N4" s="22" t="inlineStr"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J4" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="K4" s="21" t="n">
+        <v>28</v>
+      </c>
+      <c r="L4" s="22" t="n">
+        <v>0.238</v>
+      </c>
+      <c r="M4" s="22" t="n">
+        <v>0.0583</v>
+      </c>
+      <c r="N4" s="22" t="n">
+        <v>0.2963</v>
+      </c>
       <c r="O4" s="21" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="P4" s="22" t="inlineStr"/>
-      <c r="Q4" s="22" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P4" s="22" t="inlineStr">
+        <is>
+          <t>1 retry 083_chunk02 0c fixed via single-chunk re-transcribe</t>
+        </is>
+      </c>
+      <c r="Q4" s="22" t="inlineStr">
+        <is>
+          <t>2-workers parallel 741s 0 anomalies dur-aware after fix</t>
+        </is>
+      </c>
       <c r="R4" s="22" t="inlineStr">
         <is>
           <t>periapuranam/output/mei_p_porul_nayanar/tamil_real/mei_p_porul_nayanar_tamil.txt ; mei_p_porul_nayanar_english.txt</t>
@@ -6937,21 +6969,39 @@
       </c>
       <c r="I5" s="23" t="inlineStr">
         <is>
-          <t>To be done</t>
-        </is>
-      </c>
-      <c r="J5" s="21" t="inlineStr"/>
-      <c r="K5" s="21" t="inlineStr"/>
-      <c r="L5" s="22" t="inlineStr"/>
-      <c r="M5" s="22" t="inlineStr"/>
-      <c r="N5" s="22" t="inlineStr"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J5" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="K5" s="21" t="n">
+        <v>38</v>
+      </c>
+      <c r="L5" s="22" t="n">
+        <v>0.3159</v>
+      </c>
+      <c r="M5" s="22" t="n">
+        <v>0.0824</v>
+      </c>
+      <c r="N5" s="22" t="n">
+        <v>0.3983</v>
+      </c>
       <c r="O5" s="21" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="P5" s="22" t="inlineStr"/>
-      <c r="Q5" s="22" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P5" s="22" t="inlineStr">
+        <is>
+          <t>chunked translate 63k+57k 2 calls (120k &gt;30k)</t>
+        </is>
+      </c>
+      <c r="Q5" s="22" t="inlineStr">
+        <is>
+          <t>Sak 120k needs chunked translate as giants</t>
+        </is>
+      </c>
       <c r="R5" s="22" t="inlineStr">
         <is>
           <t>periapuranam/output/sakkiya_nayanar/tamil_real/sakkiya_nayanar_tamil.txt ; sakkiya_nayanar_english.txt</t>
@@ -6995,21 +7045,39 @@
       </c>
       <c r="I6" s="23" t="inlineStr">
         <is>
-          <t>To be done</t>
-        </is>
-      </c>
-      <c r="J6" s="21" t="inlineStr"/>
-      <c r="K6" s="21" t="inlineStr"/>
-      <c r="L6" s="22" t="inlineStr"/>
-      <c r="M6" s="22" t="inlineStr"/>
-      <c r="N6" s="22" t="inlineStr"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J6" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="K6" s="21" t="n">
+        <v>32</v>
+      </c>
+      <c r="L6" s="22" t="n">
+        <v>0.2873</v>
+      </c>
+      <c r="M6" s="22" t="n">
+        <v>0.0803</v>
+      </c>
+      <c r="N6" s="22" t="n">
+        <v>0.3676</v>
+      </c>
       <c r="O6" s="21" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="P6" s="22" t="inlineStr"/>
-      <c r="Q6" s="22" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P6" s="22" t="inlineStr">
+        <is>
+          <t>0 anomalies dur-aware</t>
+        </is>
+      </c>
+      <c r="Q6" s="22" t="inlineStr">
+        <is>
+          <t>2-workers parallel ThiruMoola||Tirunilakanta 13m wall</t>
+        </is>
+      </c>
       <c r="R6" s="22" t="inlineStr">
         <is>
           <t>periapuranam/output/thirumoola_deva_nayanar/tamil_real/thirumoola_deva_nayanar_tamil.txt ; thirumoola_deva_nayanar_english.txt</t>
@@ -7053,20 +7121,34 @@
       </c>
       <c r="I7" s="23" t="inlineStr">
         <is>
-          <t>To be done</t>
-        </is>
-      </c>
-      <c r="J7" s="21" t="inlineStr"/>
-      <c r="K7" s="21" t="inlineStr"/>
-      <c r="L7" s="22" t="inlineStr"/>
-      <c r="M7" s="22" t="inlineStr"/>
-      <c r="N7" s="22" t="inlineStr"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J7" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="K7" s="21" t="n">
+        <v>32</v>
+      </c>
+      <c r="L7" s="22" t="n">
+        <v>0.2703</v>
+      </c>
+      <c r="M7" s="22" t="n">
+        <v>0.0638</v>
+      </c>
+      <c r="N7" s="22" t="n">
+        <v>0.3341</v>
+      </c>
       <c r="O7" s="21" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="P7" s="22" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P7" s="22" t="inlineStr">
+        <is>
+          <t>0 anomalies</t>
+        </is>
+      </c>
       <c r="Q7" s="22" t="inlineStr"/>
       <c r="R7" s="22" t="inlineStr">
         <is>
@@ -7111,21 +7193,39 @@
       </c>
       <c r="I8" s="23" t="inlineStr">
         <is>
-          <t>To be done</t>
-        </is>
-      </c>
-      <c r="J8" s="21" t="inlineStr"/>
-      <c r="K8" s="21" t="inlineStr"/>
-      <c r="L8" s="22" t="inlineStr"/>
-      <c r="M8" s="22" t="inlineStr"/>
-      <c r="N8" s="22" t="inlineStr"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J8" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="K8" s="21" t="n">
+        <v>35</v>
+      </c>
+      <c r="L8" s="22" t="n">
+        <v>0.2714</v>
+      </c>
+      <c r="M8" s="22" t="n">
+        <v>0.06660000000000001</v>
+      </c>
+      <c r="N8" s="22" t="n">
+        <v>0.338</v>
+      </c>
       <c r="O8" s="21" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="P8" s="22" t="inlineStr"/>
-      <c r="Q8" s="22" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P8" s="22" t="inlineStr">
+        <is>
+          <t>1 HUGE 064 22k fixed 3493c</t>
+        </is>
+      </c>
+      <c r="Q8" s="22" t="inlineStr">
+        <is>
+          <t>064 22k HUGE flagged dur*20 correctly</t>
+        </is>
+      </c>
       <c r="R8" s="22" t="inlineStr">
         <is>
           <t>periapuranam/output/iyarpakai_nayanar/tamil_real/iyarpakai_nayanar_tamil.txt ; iyarpakai_nayanar_english.txt</t>
@@ -7169,20 +7269,34 @@
       </c>
       <c r="I9" s="23" t="inlineStr">
         <is>
-          <t>To be done</t>
-        </is>
-      </c>
-      <c r="J9" s="21" t="inlineStr"/>
-      <c r="K9" s="21" t="inlineStr"/>
-      <c r="L9" s="22" t="inlineStr"/>
-      <c r="M9" s="22" t="inlineStr"/>
-      <c r="N9" s="22" t="inlineStr"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J9" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="K9" s="21" t="n">
+        <v>33</v>
+      </c>
+      <c r="L9" s="22" t="n">
+        <v>0.2665</v>
+      </c>
+      <c r="M9" s="22" t="n">
+        <v>0.06859999999999999</v>
+      </c>
+      <c r="N9" s="22" t="n">
+        <v>0.3351</v>
+      </c>
       <c r="O9" s="21" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="P9" s="22" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P9" s="22" t="inlineStr">
+        <is>
+          <t>0 anomalies</t>
+        </is>
+      </c>
       <c r="Q9" s="22" t="inlineStr"/>
       <c r="R9" s="22" t="inlineStr">
         <is>

--- a/periapuranam/day_wise_plan.xlsx
+++ b/periapuranam/day_wise_plan.xlsx
@@ -41,8 +41,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="0.0000"/>
   </numFmts>
   <fonts count="13">
     <font>
@@ -278,7 +279,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -385,6 +386,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -895,16 +905,34 @@
           <t>$0.71</t>
         </is>
       </c>
-      <c r="J2" s="5" t="inlineStr"/>
-      <c r="K2" s="5" t="inlineStr"/>
-      <c r="L2" s="5" t="inlineStr"/>
-      <c r="M2" s="5" t="inlineStr"/>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>21/21</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>86 chunks (21 translate)</t>
+        </is>
+      </c>
+      <c r="M2" s="41" t="n">
+        <v>0.9644</v>
+      </c>
       <c r="N2" s="4" t="inlineStr">
         <is>
-          <t>21 output folders in day-01/ — Verify Chapter 01=1, no ==== | FLAGGED: Poyyadiai illadha Nayanar (967) WRONG CONTENT (Kootruva duplicate) — flagged in Day 1 row14, await actual source</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr"/>
+          <t>21/21 PASS Chapter 01=1 no ==== finish:stop; 1 flagged Poyyadiai WRONG (Kootruva dup) pending source</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="52" customHeight="1">
       <c r="A3" s="2" t="n">
@@ -942,16 +970,34 @@
           <t>$1.15</t>
         </is>
       </c>
-      <c r="J3" s="5" t="inlineStr"/>
-      <c r="K3" s="5" t="inlineStr"/>
-      <c r="L3" s="5" t="inlineStr"/>
-      <c r="M3" s="5" t="inlineStr"/>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>14/14</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>123 chunks (14 translate)</t>
+        </is>
+      </c>
+      <c r="M3" s="41" t="n">
+        <v>1.3558</v>
+      </c>
       <c r="N3" s="4" t="inlineStr">
         <is>
-          <t>14 stories Thillai Vazh Anthanar 3 files -&gt; C01..03</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr"/>
+          <t>14/14 PASS Chapter 02/03=ok no ====; 2 anomalies KazharChinga 41832 + Thillai 0-char deferred; AdhiBaththa INFO duplicate fid</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="52" customHeight="1">
       <c r="A4" s="2" t="n">
@@ -1004,7 +1050,7 @@
           <t>~5.2h seq (217 chunks) + 11 translate</t>
         </is>
       </c>
-      <c r="M4" s="5" t="n">
+      <c r="M4" s="41" t="n">
         <v>2.30449</v>
       </c>
       <c r="N4" s="4" t="inlineStr">
@@ -1051,23 +1097,27 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
+          <t>$1.88</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="J5" s="5" t="inlineStr">
+      <c r="K5" s="5" t="inlineStr">
         <is>
           <t>56/56</t>
         </is>
       </c>
-      <c r="K5" s="5" t="inlineStr">
+      <c r="L5" s="5" t="inlineStr">
         <is>
           <t>223 chunks 2-workers + fixes</t>
         </is>
       </c>
-      <c r="L5" s="5" t="n">
+      <c r="M5" s="41" t="n">
         <v>2.3147</v>
       </c>
-      <c r="M5" s="5" t="inlineStr"/>
       <c r="N5" s="4" t="inlineStr">
         <is>
           <t>Day4 7/7 PASS Chapter N==files no ====; ThiruMoola/Tiru 0 anomalies dur-aware; Mei 083 fixed; Iyar HUGE fixed; Sak chunked translate</t>
@@ -1115,16 +1165,34 @@
           <t>$2.45</t>
         </is>
       </c>
-      <c r="J6" s="5" t="inlineStr"/>
-      <c r="K6" s="5" t="inlineStr"/>
-      <c r="L6" s="5" t="inlineStr"/>
-      <c r="M6" s="5" t="inlineStr"/>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="inlineStr">
+        <is>
+          <t>34/73 (3/6 stories)</t>
+        </is>
+      </c>
+      <c r="L6" s="5" t="inlineStr">
+        <is>
+          <t>120ch 3-parallel 38m +524 fix</t>
+        </is>
+      </c>
+      <c r="M6" s="41" t="n">
+        <v>1.2142</v>
+      </c>
       <c r="N6" s="4" t="inlineStr">
         <is>
-          <t>6 stories Siruthonda 13 files</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr"/>
+          <t>Murthi/Tiru/Appoothi DONE 0 anomalies (1 fixed), remaining Amar/Eri/Siruthonda 39F via batch wrapper</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="52" customHeight="1">
       <c r="A7" s="2" t="n">
@@ -7479,21 +7547,41 @@
       </c>
       <c r="I3" s="23" t="inlineStr">
         <is>
-          <t>To be done</t>
-        </is>
-      </c>
-      <c r="J3" s="21" t="inlineStr"/>
-      <c r="K3" s="21" t="inlineStr"/>
-      <c r="L3" s="22" t="inlineStr"/>
-      <c r="M3" s="22" t="inlineStr"/>
-      <c r="N3" s="22" t="inlineStr"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J3" s="21" t="inlineStr">
+        <is>
+          <t>11/11</t>
+        </is>
+      </c>
+      <c r="K3" s="42" t="n">
+        <v>43</v>
+      </c>
+      <c r="L3" s="43" t="n">
+        <v>0.3516</v>
+      </c>
+      <c r="M3" s="43" t="n">
+        <v>0.08450000000000001</v>
+      </c>
+      <c r="N3" s="43" t="n">
+        <v>0.4361</v>
+      </c>
       <c r="O3" s="21" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P3" s="22" t="inlineStr"/>
-      <c r="Q3" s="22" t="inlineStr"/>
+      <c r="P3" s="22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q3" s="22" t="inlineStr">
+        <is>
+          <t>3-parallel 38m wall 0 anomalies 2103s no ==== Chapter 11/11</t>
+        </is>
+      </c>
       <c r="R3" s="22" t="inlineStr">
         <is>
           <t>periapuranam/output/murthi_nayanar/tamil_real/murthi_nayanar_tamil.txt ; murthi_nayanar_english.txt</t>
@@ -7537,21 +7625,41 @@
       </c>
       <c r="I4" s="23" t="inlineStr">
         <is>
-          <t>To be done</t>
-        </is>
-      </c>
-      <c r="J4" s="21" t="inlineStr"/>
-      <c r="K4" s="21" t="inlineStr"/>
-      <c r="L4" s="22" t="inlineStr"/>
-      <c r="M4" s="22" t="inlineStr"/>
-      <c r="N4" s="22" t="inlineStr"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J4" s="21" t="inlineStr">
+        <is>
+          <t>11/11</t>
+        </is>
+      </c>
+      <c r="K4" s="42" t="n">
+        <v>35</v>
+      </c>
+      <c r="L4" s="43" t="n">
+        <v>0.2778</v>
+      </c>
+      <c r="M4" s="43" t="n">
+        <v>0.0675</v>
+      </c>
+      <c r="N4" s="43" t="n">
+        <v>0.3453</v>
+      </c>
       <c r="O4" s="21" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P4" s="22" t="inlineStr"/>
-      <c r="Q4" s="22" t="inlineStr"/>
+      <c r="P4" s="22" t="inlineStr">
+        <is>
+          <t>1 re-transcribe 524/3 0-&gt;397c</t>
+        </is>
+      </c>
+      <c r="Q4" s="22" t="inlineStr">
+        <is>
+          <t>30s tail fixed 0 anomalies now 1799s no ====</t>
+        </is>
+      </c>
       <c r="R4" s="22" t="inlineStr">
         <is>
           <t>periapuranam/output/tiruneelanakkar_nayanar/tamil_real/tiruneelanakkar_nayanar_tamil.txt ; tiruneelanakkar_nayanar_english.txt</t>
@@ -7595,21 +7703,41 @@
       </c>
       <c r="I5" s="23" t="inlineStr">
         <is>
-          <t>To be done</t>
-        </is>
-      </c>
-      <c r="J5" s="21" t="inlineStr"/>
-      <c r="K5" s="21" t="inlineStr"/>
-      <c r="L5" s="22" t="inlineStr"/>
-      <c r="M5" s="22" t="inlineStr"/>
-      <c r="N5" s="22" t="inlineStr"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J5" s="21" t="inlineStr">
+        <is>
+          <t>12/12</t>
+        </is>
+      </c>
+      <c r="K5" s="42" t="n">
+        <v>42</v>
+      </c>
+      <c r="L5" s="43" t="n">
+        <v>0.3484</v>
+      </c>
+      <c r="M5" s="43" t="n">
+        <v>0.0844</v>
+      </c>
+      <c r="N5" s="43" t="n">
+        <v>0.4328</v>
+      </c>
       <c r="O5" s="21" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P5" s="22" t="inlineStr"/>
-      <c r="Q5" s="22" t="inlineStr"/>
+      <c r="P5" s="22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" s="22" t="inlineStr">
+        <is>
+          <t>3-parallel 0 anomalies 2038s no ==== Chapter 12/12</t>
+        </is>
+      </c>
       <c r="R5" s="22" t="inlineStr">
         <is>
           <t>periapuranam/output/appoothi_adikal_nayanar/tamil_real/appoothi_adikal_nayanar_tamil.txt ; appoothi_adikal_nayanar_english.txt</t>

--- a/periapuranam/day_wise_plan.xlsx
+++ b/periapuranam/day_wise_plan.xlsx
@@ -1167,30 +1167,30 @@
       </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="K6" s="5" t="inlineStr">
         <is>
-          <t>34/73 (3/6 stories)</t>
+          <t>73/73 (6/6 stories)</t>
         </is>
       </c>
       <c r="L6" s="5" t="inlineStr">
         <is>
-          <t>120ch 3-parallel 38m +524 fix</t>
+          <t>269ch 3-parallel 38m + Tamil fix 4ch 4m + English chunked 9ch 10m (52m wall)</t>
         </is>
       </c>
       <c r="M6" s="41" t="n">
-        <v>1.2142</v>
+        <v>2.4193</v>
       </c>
       <c r="N6" s="4" t="inlineStr">
         <is>
-          <t>Murthi/Tiru/Appoothi DONE 0 anomalies (1 fixed), remaining Amar/Eri/Siruthonda 39F via batch wrapper</t>
+          <t>6/6 DONE 11+11+12+13+13+13 ch 43+35+42+48+53+48 no ==== Ch 11/11 12/12 13/13/13 fix 095 HUGE 43k-&gt;176c re-download +3 tails; English chunked 3x3 english_real stop</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -7781,24 +7781,44 @@
       </c>
       <c r="I6" s="23" t="inlineStr">
         <is>
-          <t>To be done</t>
-        </is>
-      </c>
-      <c r="J6" s="21" t="inlineStr"/>
-      <c r="K6" s="21" t="inlineStr"/>
-      <c r="L6" s="22" t="inlineStr"/>
-      <c r="M6" s="22" t="inlineStr"/>
-      <c r="N6" s="22" t="inlineStr"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J6" s="21" t="inlineStr">
+        <is>
+          <t>13/13</t>
+        </is>
+      </c>
+      <c r="K6" s="21" t="n">
+        <v>48</v>
+      </c>
+      <c r="L6" s="22" t="n">
+        <v>0.2747</v>
+      </c>
+      <c r="M6" s="22" t="n">
+        <v>0.0905</v>
+      </c>
+      <c r="N6" s="22" t="n">
+        <v>0.3652</v>
+      </c>
       <c r="O6" s="21" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P6" s="22" t="inlineStr"/>
-      <c r="Q6" s="22" t="inlineStr"/>
+      <c r="P6" s="22" t="inlineStr">
+        <is>
+          <t>1 fix 095 HUGE 43198-&gt;176c re-download 14.2M + chunk 43k-&gt;176c</t>
+        </is>
+      </c>
+      <c r="Q6" s="22" t="inlineStr">
+        <is>
+          <t>3-parallel then Tamil fix + English chunked 3/3 58857+48347+25003 english_real 0 anomalies</t>
+        </is>
+      </c>
       <c r="R6" s="22" t="inlineStr">
         <is>
-          <t>periapuranam/output/amar_niti_nayanar/tamil_real/amar_niti_nayanar_tamil.txt ; amar_niti_nayanar_english.txt</t>
+          <t>periapuranam/output/day-05/amar_niti_nayanar/tamil_real/amar_niti_nayanar_tamil.txt ; amar_niti_nayanar_english.txt ; english_real/3 chunks</t>
         </is>
       </c>
     </row>
@@ -7839,24 +7859,44 @@
       </c>
       <c r="I7" s="23" t="inlineStr">
         <is>
-          <t>To be done</t>
-        </is>
-      </c>
-      <c r="J7" s="21" t="inlineStr"/>
-      <c r="K7" s="21" t="inlineStr"/>
-      <c r="L7" s="22" t="inlineStr"/>
-      <c r="M7" s="22" t="inlineStr"/>
-      <c r="N7" s="22" t="inlineStr"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J7" s="21" t="inlineStr">
+        <is>
+          <t>13/13</t>
+        </is>
+      </c>
+      <c r="K7" s="21" t="n">
+        <v>53</v>
+      </c>
+      <c r="L7" s="22" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="M7" s="22" t="n">
+        <v>0.1054</v>
+      </c>
+      <c r="N7" s="22" t="n">
+        <v>0.4384</v>
+      </c>
       <c r="O7" s="21" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P7" s="22" t="inlineStr"/>
-      <c r="Q7" s="22" t="inlineStr"/>
+      <c r="P7" s="22" t="inlineStr">
+        <is>
+          <t>1 fix 111 TINY 7-&gt;81c</t>
+        </is>
+      </c>
+      <c r="Q7" s="22" t="inlineStr">
+        <is>
+          <t>English chunked 3/3 52962+57487+44760 0 anomalies</t>
+        </is>
+      </c>
       <c r="R7" s="22" t="inlineStr">
         <is>
-          <t>periapuranam/output/eri_pattha_nayanar/tamil_real/eri_pattha_nayanar_tamil.txt ; eri_pattha_nayanar_english.txt</t>
+          <t>periapuranam/output/day-05/eri_pattha_nayanar/tamil_real/eri_pattha_nayanar_tamil.txt ; eri_pattha_nayanar_english.txt ; english_real/3 chunks</t>
         </is>
       </c>
     </row>
@@ -7897,24 +7937,44 @@
       </c>
       <c r="I8" s="23" t="inlineStr">
         <is>
-          <t>To be done</t>
-        </is>
-      </c>
-      <c r="J8" s="21" t="inlineStr"/>
-      <c r="K8" s="21" t="inlineStr"/>
-      <c r="L8" s="22" t="inlineStr"/>
-      <c r="M8" s="22" t="inlineStr"/>
-      <c r="N8" s="22" t="inlineStr"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J8" s="21" t="inlineStr">
+        <is>
+          <t>13/13</t>
+        </is>
+      </c>
+      <c r="K8" s="21" t="n">
+        <v>48</v>
+      </c>
+      <c r="L8" s="22" t="n">
+        <v>0.3046</v>
+      </c>
+      <c r="M8" s="22" t="n">
+        <v>0.0969</v>
+      </c>
+      <c r="N8" s="22" t="n">
+        <v>0.4015</v>
+      </c>
       <c r="O8" s="21" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P8" s="22" t="inlineStr"/>
-      <c r="Q8" s="22" t="inlineStr"/>
+      <c r="P8" s="22" t="inlineStr">
+        <is>
+          <t>2 fix 926 TINY 7-&gt;89c + 928 EMPTY 0-&gt;544c</t>
+        </is>
+      </c>
+      <c r="Q8" s="22" t="inlineStr">
+        <is>
+          <t>English chunked 3/3 44444+55733+42806 0 anomalies</t>
+        </is>
+      </c>
       <c r="R8" s="22" t="inlineStr">
         <is>
-          <t>periapuranam/output/siruthonda_nayanar/tamil_real/siruthonda_nayanar_tamil.txt ; siruthonda_nayanar_english.txt</t>
+          <t>periapuranam/output/day-05/siruthonda_nayanar/tamil_real/siruthonda_nayanar_tamil.txt ; siruthonda_nayanar_english.txt ; english_real/3 chunks</t>
         </is>
       </c>
     </row>

--- a/periapuranam/day_wise_plan.xlsx
+++ b/periapuranam/day_wise_plan.xlsx
@@ -761,7 +761,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O13"/>
+  <dimension ref="A1:P13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1231,15 +1231,34 @@
         </is>
       </c>
       <c r="J7" s="5" t="inlineStr"/>
-      <c r="K7" s="5" t="inlineStr"/>
-      <c r="L7" s="5" t="inlineStr"/>
-      <c r="M7" s="5" t="inlineStr"/>
-      <c r="N7" s="4" t="inlineStr">
-        <is>
-          <t>Kannappa 32 -&gt; C01..32 Kazharitrarivar 28</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr"/>
+      <c r="K7" s="5" t="inlineStr">
+        <is>
+          <t>36/96 (2/4 stories)</t>
+        </is>
+      </c>
+      <c r="L7" s="5" t="inlineStr">
+        <is>
+          <t>130/336 (66+64)</t>
+        </is>
+      </c>
+      <c r="M7" s="5" t="inlineStr">
+        <is>
+          <t>50m wall (40.5m Phase A+B + 9.6m Phase C)</t>
+        </is>
+      </c>
+      <c r="N7" s="4" t="n">
+        <v>1.3431</v>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>Partial — 2/4 Done, 251/261 tails 0 flagged, 246 HUGE fixed, 493 fixed, 2-parallel, download retry 120s 3x</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="52" customHeight="1">
       <c r="A8" s="2" t="n">
@@ -8153,24 +8172,44 @@
       </c>
       <c r="I3" s="23" t="inlineStr">
         <is>
-          <t>To be done</t>
-        </is>
-      </c>
-      <c r="J3" s="21" t="inlineStr"/>
-      <c r="K3" s="21" t="inlineStr"/>
-      <c r="L3" s="22" t="inlineStr"/>
-      <c r="M3" s="22" t="inlineStr"/>
-      <c r="N3" s="22" t="inlineStr"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J3" s="21" t="inlineStr">
+        <is>
+          <t>18/18</t>
+        </is>
+      </c>
+      <c r="K3" s="21" t="n">
+        <v>66</v>
+      </c>
+      <c r="L3" s="22" t="n">
+        <v>0.575</v>
+      </c>
+      <c r="M3" s="22" t="n">
+        <v>0.1376</v>
+      </c>
+      <c r="N3" s="22" t="n">
+        <v>0.7126</v>
+      </c>
       <c r="O3" s="21" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P3" s="22" t="inlineStr"/>
-      <c r="Q3" s="22" t="inlineStr"/>
+      <c r="P3" s="22" t="inlineStr">
+        <is>
+          <t>2 HUGE 246c02 37k len 246c03 50k len (empty mp3 395B, header 1064s vs valid 510s) removed; 2 EMPTY 251c03 0 dur75 261c04 0 dur34 tail silence; 1 download retry 246 17M-&gt;8M</t>
+        </is>
+      </c>
+      <c r="Q3" s="22" t="inlineStr">
+        <is>
+          <t>2-parallel 40.5m wall 206K Tamil 566KB 18ch no ====; English chunked 4x60K 207K bilingual 773K 5.1m; 246 re-merged 255K-&gt;5827</t>
+        </is>
+      </c>
       <c r="R3" s="22" t="inlineStr">
         <is>
-          <t>periapuranam/output/chandesura_nayanar/tamil_real/chandesura_nayanar_tamil.txt ; chandesura_nayanar_english.txt</t>
+          <t>periapuranam/output/day-06/chandesura_nayanar/tamil_real/chandesura_nayanar_tamil.txt ; chandesura_nayanar_english.txt ; english_real/4 chunks</t>
         </is>
       </c>
     </row>
@@ -8211,24 +8250,44 @@
       </c>
       <c r="I4" s="23" t="inlineStr">
         <is>
-          <t>To be done</t>
-        </is>
-      </c>
-      <c r="J4" s="21" t="inlineStr"/>
-      <c r="K4" s="21" t="inlineStr"/>
-      <c r="L4" s="22" t="inlineStr"/>
-      <c r="M4" s="22" t="inlineStr"/>
-      <c r="N4" s="22" t="inlineStr"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J4" s="21" t="inlineStr">
+        <is>
+          <t>18/18</t>
+        </is>
+      </c>
+      <c r="K4" s="21" t="n">
+        <v>64</v>
+      </c>
+      <c r="L4" s="22" t="n">
+        <v>0.4998</v>
+      </c>
+      <c r="M4" s="22" t="n">
+        <v>0.1307</v>
+      </c>
+      <c r="N4" s="22" t="n">
+        <v>0.6304999999999999</v>
+      </c>
       <c r="O4" s="21" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P4" s="22" t="inlineStr"/>
-      <c r="Q4" s="22" t="inlineStr"/>
+      <c r="P4" s="22" t="inlineStr">
+        <is>
+          <t>1 TINY 493c01 22-&gt;3438 re-transcribed (ConnectionReset 10054 retry1); 0 download failures after retry patch</t>
+        </is>
+      </c>
+      <c r="Q4" s="22" t="inlineStr">
+        <is>
+          <t>2-parallel 40.5m wall 198K Tamil 543KB 18ch no ====; English chunked 4x60K 191K bilingual 736K 4.5m</t>
+        </is>
+      </c>
       <c r="R4" s="22" t="inlineStr">
         <is>
-          <t>periapuranam/output/karaikal_ammaiyaar/tamil_real/karaikal_ammaiyaar_tamil.txt ; karaikal_ammaiyaar_english.txt</t>
+          <t>periapuranam/output/day-06/karaikal_ammaiyaar/tamil_real/karaikal_ammaiyaar_tamil.txt ; karaikal_ammaiyaar_english.txt ; english_real/4 chunks</t>
         </is>
       </c>
     </row>

--- a/periapuranam/day_wise_plan.xlsx
+++ b/periapuranam/day_wise_plan.xlsx
@@ -1230,28 +1230,32 @@
           <t>$3.24</t>
         </is>
       </c>
-      <c r="J7" s="5" t="inlineStr"/>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
       <c r="K7" s="5" t="inlineStr">
         <is>
-          <t>36/96 (2/4 stories)</t>
+          <t>96/96 (4/4 stories)</t>
         </is>
       </c>
       <c r="L7" s="5" t="inlineStr">
         <is>
-          <t>130/336 (66+64)</t>
-        </is>
-      </c>
-      <c r="M7" s="5" t="inlineStr">
-        <is>
-          <t>50m wall (40.5m Phase A+B + 9.6m Phase C)</t>
-        </is>
-      </c>
-      <c r="N7" s="4" t="n">
-        <v>1.3431</v>
+          <t>362 chunks (68+64+90+140) + 15 translate (4+4+6+9) ~177m wall (50m earlier +12.4m A+95m B+20m C)</t>
+        </is>
+      </c>
+      <c r="M7" s="5" t="n">
+        <v>3.835</v>
+      </c>
+      <c r="N7" s="4" t="inlineStr">
+        <is>
+          <t>4/4 DONE 18+18+28+32 ch 68+64+90+140 no ==== Ch 18/18 28/28 32/32; Kazhar 0 anomalies clean, Kannappa 2 tails fixed 128 0-&gt;2312 147 7-&gt;774 re-merged 435893; English chunked 4+4+6+9 sequential 60K stop; Day6 heritage 96/96 DONE</t>
+        </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>Partial — 2/4 Done, 251/261 tails 0 flagged, 246 HUGE fixed, 493 fixed, 2-parallel, download retry 120s 3x</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">

--- a/periapuranam/day_wise_plan.xlsx
+++ b/periapuranam/day_wise_plan.xlsx
@@ -1246,7 +1246,7 @@
         </is>
       </c>
       <c r="M7" s="5" t="n">
-        <v>3.835</v>
+        <v>3.6721</v>
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
@@ -8332,24 +8332,44 @@
       </c>
       <c r="I5" s="23" t="inlineStr">
         <is>
-          <t>To be done</t>
-        </is>
-      </c>
-      <c r="J5" s="21" t="inlineStr"/>
-      <c r="K5" s="21" t="inlineStr"/>
-      <c r="L5" s="22" t="inlineStr"/>
-      <c r="M5" s="22" t="inlineStr"/>
-      <c r="N5" s="22" t="inlineStr"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J5" s="21" t="inlineStr">
+        <is>
+          <t>28/28</t>
+        </is>
+      </c>
+      <c r="K5" s="21" t="n">
+        <v>90</v>
+      </c>
+      <c r="L5" s="22" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="M5" s="22" t="n">
+        <v>0.2021</v>
+      </c>
+      <c r="N5" s="22" t="n">
+        <v>0.9221</v>
+      </c>
       <c r="O5" s="21" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P5" s="22" t="inlineStr"/>
-      <c r="Q5" s="22" t="inlineStr"/>
+      <c r="P5" s="22" t="inlineStr">
+        <is>
+          <t>0 anomalies; Phase A 28/28 12.4m 2-parallel; Phase B 90ch 95m 4-parallel resume (Budget 403 monthly fix); 8 empty mp3 skipped (395B)</t>
+        </is>
+      </c>
+      <c r="Q5" s="22" t="inlineStr">
+        <is>
+          <t>12.4m A + 95m B wall 287K Tamil 789KB 28ch no ====; English chunked 6x60K 292K bilingual 1081K 8.1m sequential</t>
+        </is>
+      </c>
       <c r="R5" s="22" t="inlineStr">
         <is>
-          <t>periapuranam/output/kazharitrarivar_nayanar/tamil_real/kazharitrarivar_nayanar_tamil.txt ; kazharitrarivar_nayanar_english.txt</t>
+          <t>periapuranam/output/day-06/kazharitrarivar_nayanar/tamil_real/kazharitrarivar_nayanar_tamil.txt ; english_real/6 chunks; kazharitrarivar_nayanar_english.txt</t>
         </is>
       </c>
     </row>
@@ -8390,24 +8410,44 @@
       </c>
       <c r="I6" s="23" t="inlineStr">
         <is>
-          <t>To be done</t>
-        </is>
-      </c>
-      <c r="J6" s="21" t="inlineStr"/>
-      <c r="K6" s="21" t="inlineStr"/>
-      <c r="L6" s="22" t="inlineStr"/>
-      <c r="M6" s="22" t="inlineStr"/>
-      <c r="N6" s="22" t="inlineStr"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J6" s="21" t="inlineStr">
+        <is>
+          <t>32/32</t>
+        </is>
+      </c>
+      <c r="K6" s="21" t="n">
+        <v>140</v>
+      </c>
+      <c r="L6" s="22" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="M6" s="22" t="n">
+        <v>0.2869</v>
+      </c>
+      <c r="N6" s="22" t="n">
+        <v>1.4069</v>
+      </c>
       <c r="O6" s="21" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P6" s="22" t="inlineStr"/>
-      <c r="Q6" s="22" t="inlineStr"/>
+      <c r="P6" s="22" t="inlineStr">
+        <is>
+          <t>2 tails fixed 128 EMPTY 0-&gt;2312 dur225 147 TINY 7-&gt;774 dur62 re-merged 435893; Phase B 95m 4-parallel resume Budget 403</t>
+        </is>
+      </c>
+      <c r="Q6" s="22" t="inlineStr">
+        <is>
+          <t>12.4m A + 95m B wall 435K Tamil 1193KB 32ch no ==== anomalies 0 after fix; English chunked 9x60K 421K bilingual 1615K 11.8m sequential; arrow cp1252 fix</t>
+        </is>
+      </c>
       <c r="R6" s="22" t="inlineStr">
         <is>
-          <t>periapuranam/output/kannappa_nayanar/tamil_real/kannappa_nayanar_tamil.txt ; kannappa_nayanar_english.txt</t>
+          <t>periapuranam/output/day-06/kannappa_nayanar/tamil_real/kannappa_nayanar_tamil.txt ; english_real/9 chunks; kannappa_nayanar_english.txt</t>
         </is>
       </c>
     </row>

--- a/periapuranam/day_wise_plan.xlsx
+++ b/periapuranam/day_wise_plan.xlsx
@@ -41,9 +41,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
+    <numFmt numFmtId="166" formatCode="0.000"/>
   </numFmts>
   <fonts count="13">
     <font>
@@ -279,7 +280,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -394,6 +395,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1300,16 +1304,34 @@
           <t>$2.43</t>
         </is>
       </c>
-      <c r="J8" s="5" t="inlineStr"/>
-      <c r="K8" s="5" t="inlineStr"/>
-      <c r="L8" s="5" t="inlineStr"/>
-      <c r="M8" s="5" t="inlineStr"/>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="inlineStr">
+        <is>
+          <t>36/72 (1/2 stories)</t>
+        </is>
+      </c>
+      <c r="L8" s="5" t="inlineStr">
+        <is>
+          <t>129ch + 8 translate ~75m wall (8m A +55m B +12m C)</t>
+        </is>
+      </c>
+      <c r="M8" s="41" t="n">
+        <v>1.3742</v>
+      </c>
       <c r="N8" s="4" t="inlineStr">
         <is>
-          <t>36-file stories: check Chapter count Sundarar discuss separately</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr"/>
+          <t>Tiruk Kurippu 36/36 DONE 129ch 399540 Tamil 389965 English no ==== Ch36 1 HUGE fixed 225-&gt;10546; Sundarar DEFERRED per owner</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="52" customHeight="1">
       <c r="A9" s="2" t="n">
@@ -1706,7 +1728,7 @@
       </c>
       <c r="I3" s="23" t="inlineStr">
         <is>
-          <t>To be done</t>
+          <t>Deferred</t>
         </is>
       </c>
       <c r="J3" s="21" t="inlineStr"/>
@@ -1719,8 +1741,16 @@
           <t>No</t>
         </is>
       </c>
-      <c r="P3" s="22" t="inlineStr"/>
-      <c r="Q3" s="22" t="inlineStr"/>
+      <c r="P3" s="22" t="inlineStr">
+        <is>
+          <t>DEFERRED until further notice per owner 2026-09-18</t>
+        </is>
+      </c>
+      <c r="Q3" s="22" t="inlineStr">
+        <is>
+          <t>Sundarar 36 files deferred — awaiting sequence determination for remaining files beyond day-07</t>
+        </is>
+      </c>
       <c r="R3" s="22" t="inlineStr">
         <is>
           <t>periapuranam/output/sundarar/tamil_real/sundarar_tamil.txt ; sundarar_english.txt</t>
@@ -1764,24 +1794,44 @@
       </c>
       <c r="I4" s="23" t="inlineStr">
         <is>
-          <t>To be done</t>
-        </is>
-      </c>
-      <c r="J4" s="21" t="inlineStr"/>
-      <c r="K4" s="21" t="inlineStr"/>
-      <c r="L4" s="22" t="inlineStr"/>
-      <c r="M4" s="22" t="inlineStr"/>
-      <c r="N4" s="22" t="inlineStr"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J4" s="21" t="inlineStr">
+        <is>
+          <t>36/36</t>
+        </is>
+      </c>
+      <c r="K4" s="21" t="n">
+        <v>129</v>
+      </c>
+      <c r="L4" s="44" t="n">
+        <v>1.107</v>
+      </c>
+      <c r="M4" s="44" t="n">
+        <v>0.267</v>
+      </c>
+      <c r="N4" s="44" t="n">
+        <v>1.374</v>
+      </c>
       <c r="O4" s="21" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P4" s="22" t="inlineStr"/>
-      <c r="Q4" s="22" t="inlineStr"/>
+      <c r="P4" s="22" t="inlineStr">
+        <is>
+          <t>1 HUGE 225c03 43k 1s hallucination beyond valid audio 901s removed re-merged 10546 vs 54184 (cost 0.029); 1 TINY 235c03 17 accepted valid Thiruchitrambalam; ch17 retrans diff &lt;50 stable</t>
+        </is>
+      </c>
+      <c r="Q4" s="22" t="inlineStr">
+        <is>
+          <t>3-phase A 36/36 8m B 129ch 55m C 8ch 12m wall ~75m 399540 Tamil 1096KB 389965 English 390KB bilingual 1486KB no ==== Ch36; ch17 fixed tail silence; english chunked 8x60K stop (3 cached +5 new)</t>
+        </is>
+      </c>
       <c r="R4" s="22" t="inlineStr">
         <is>
-          <t>periapuranam/output/tiruk_kurippu_tonda_nayanar/tamil_real/tiruk_kurippu_tonda_nayanar_tamil.txt ; tiruk_kurippu_tonda_nayanar_english.txt</t>
+          <t>periapuranam/output/day-07/tiruk_kurippu_tonda_nayanar/tamil_real/tiruk_kurippu_tonda_nayanar_tamil.txt ; tiruk_kurippu_tonda_nayanar_english.txt ; english_real/8 chunks</t>
         </is>
       </c>
     </row>
